--- a/docs/medsignal_test_scenarios.xlsx
+++ b/docs/medsignal_test_scenarios.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Master Catalogue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary by Component" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Catalogue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary by Component" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,7 +66,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +116,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCDD2"/>
+        <bgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -189,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -251,6 +263,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -640,10 +654,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Happy Paths  |  Sad Paths  |  Edge Cases    Unit + Integration</t>
-        </is>
-      </c>
-    </row>
+          <t>Positive Scenarios  |  Negative Scenarios  |  Edge Cases    Unit + Integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -719,7 +734,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -762,7 +777,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -795,7 +810,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>test_borderline_prr_signal</t>
+          <t>test_borderline_prr</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -852,7 +867,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -938,7 +953,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -985,7 +1000,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1028,7 +1043,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1048,99 +1063,99 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A1-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Agent 1 – Signal Detector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unit/test_agent1.py</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>test_validate_queries_rejects_short_queries</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Queries with fewer than 6 words fail _validate_queries; queries with exactly 6 words pass (MIN_QUERY_WORDS=6 boundary).</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>Negative Scenario</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MIN_QUERY_WORDS=6 boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>A2-01</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>test_lit_score_empty</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Empty abstracts list returns LitScore = 0.0 exactly.</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>A2-02</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Agent 2 – Literature Retriever</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_agent2.py</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>test_lit_score_five_perfect</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>5 HNSW abstracts with similarity=0.95 produce LitScore &gt; 0.9 (expected ~0.965).</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Verifies HNSW relevance weighting</t>
-        </is>
-      </c>
+      <c r="I14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>A2-03</t>
+          <t>A2-02</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1155,17 +1170,17 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>test_lit_score_one_lower_than_five</t>
+          <t>test_lit_score_five_perfect</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1 abstract scores lower than 5 abstracts at identical similarity — volume component matters.</t>
+          <t>5 HNSW abstracts with similarity=0.95 produce LitScore &gt; 0.9 (expected ~0.965).</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1178,12 +1193,16 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Verifies HNSW relevance weighting</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>A2-04</t>
+          <t>A2-03</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1198,17 +1217,17 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>test_rrf_multi_query_wins</t>
+          <t>test_lit_score_one_lower_than_five</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Paper appearing in 2 query result sets ranks above paper appearing in only 1.</t>
+          <t>1 abstract scores lower than 5 abstracts at identical similarity — volume component matters.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1221,16 +1240,12 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Core RRF logic</t>
-        </is>
-      </c>
+      <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A2-05</t>
+          <t>A2-04</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1245,17 +1260,17 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>test_rrf_no_duplicates</t>
+          <t>test_rrf_multi_query_wins</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Same PMID from two result sets appears exactly once in fused output.</t>
+          <t>Paper appearing in 2 query result sets ranks above paper appearing in only 1.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1270,14 +1285,14 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>De-duplication</t>
+          <t>Core RRF logic</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A2-06</t>
+          <t>A2-05</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1292,17 +1307,17 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>test_rrf_keeps_best_similarity</t>
+          <t>test_rrf_no_duplicates</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>When same paper appears in two result sets, the entry with the lowest distance is kept.</t>
+          <t>Same PMID from two result sets appears exactly once in fused output.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1315,12 +1330,16 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>De-duplication</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A2-07</t>
+          <t>A2-06</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1335,17 +1354,17 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>test_rrf_hnsw_and_bm25_same_paper_scores_highest</t>
+          <t>test_rrf_keeps_best_similarity</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Paper found by BOTH HNSW and BM25 ranks above papers found by only one retriever.</t>
+          <t>When same paper appears in two result sets, the entry with the lowest distance is kept.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1358,282 +1377,282 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Hybrid retrieval</t>
-        </is>
-      </c>
+      <c r="I19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>A2-07</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Agent 2 – Literature Retriever</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>unit/test_agent2.py</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>test_rrf_hnsw_and_bm25_same_paper_scores_highest</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Paper found by BOTH HNSW and BM25 ranks above papers found by only one retriever.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Hybrid retrieval</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>A2-08</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>integration/test_agent2.py</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>test_chromadb_loaded</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>ChromaDB must contain &gt;= 1,800 abstracts before any live retrieval test proceeds.</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Precondition check</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unit/test_agent2.py</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>test_lit_score_bm25_only_uses_fallback_relevance</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BM25-only abstracts (no HNSW match) use BM25_ONLY_RELEVANCE_FALLBACK=0.65 for relevance; lit_score = 0.65x0.70 + volume x0.30.</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BM25 fallback path</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A2-09</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>integration/test_agent2.py</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>test_dupilumab_conjunctivitis</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Live hybrid retrieval for dupilumab x conjunctivitis returns &gt;= 3 abstracts above the 0.60 cosine threshold.</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Golden signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A2-10</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Agent 2 – Literature Retriever</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>integration/test_agent2.py</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>test_gabapentin_respiratory</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Live hybrid retrieval for gabapentin x respiratory arrest returns valid results.</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unit/test_agent2.py</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>test_lit_score_bm25_counts_for_volume_not_relevance</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mixed HNSW+BM25 abstracts: BM25 increases volume score but only HNSW cosine similarity contributes to relevance.</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Hybrid volume effect</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>A2-10</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Agent 2 – Literature Retriever</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_agent2.py</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>test_chromadb_loaded</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>ChromaDB must contain &gt;= 1,800 abstracts before any live retrieval test proceeds.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Precondition check</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>A2-11</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>integration/test_agent2.py</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>test_bm25_finds_different_papers_than_hnsw</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>BM25 and HNSW return at least some non-overlapping papers, confirming complementary retrieval value.</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>test_dupilumab_conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Live hybrid retrieval for dupilumab x conjunctivitis returns &gt;= 3 abstracts above the 0.60 cosine threshold.</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Hybrid diversity</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>A2-12</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Agent 2 – Literature Retriever</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>integration/test_agent2.py</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>test_empty_queries_graceful</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>Agent 2 handles empty query list (Agent 1 failure scenario) without crashing — returns empty list.</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Upstream Failure</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Graceful degradation</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Golden signal</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>A3-01</t>
+          <t>A2-12</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Agent 3 – Assessor</t>
+          <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>unit/test_agent3.py</t>
+          <t>integration/test_agent2.py</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>test_priority_tier_p1</t>
+          <t>test_gabapentin_respiratory</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>stat_score &gt;= 0.7 AND lit_score &gt;= 0.5 produces priority = P1.</t>
+          <t>Live hybrid retrieval for gabapentin x respiratory arrest returns valid results.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>live</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
@@ -1641,93 +1660,101 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>A3-02</t>
+          <t>A2-13</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Agent 3 – Assessor</t>
+          <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>unit/test_agent3.py</t>
+          <t>integration/test_agent2.py</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>test_priority_tier_p2</t>
+          <t>test_bm25_finds_different_papers_than_hnsw</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>stat_score &gt;= 0.7 AND lit_score &lt; 0.5 produces priority = P2.</t>
+          <t>BM25 and HNSW return at least some non-overlapping papers, confirming complementary retrieval value.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Hybrid diversity</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A3-03</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Agent 3 – Assessor</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_agent3.py</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>test_priority_tier_p3</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>stat_score &lt; 0.7 AND lit_score &gt;= 0.5 produces priority = P3.</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>A2-14</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Agent 2 – Literature Retriever</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>integration/test_agent2.py</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>test_empty_queries_graceful</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Agent 2 handles empty query list (Agent 1 failure scenario) without crashing — returns empty list.</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Upstream Failure</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Graceful degradation</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>A3-04</t>
+          <t>A3-01</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1742,17 +1769,17 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>test_priority_tier_p4</t>
+          <t>test_priority_tier_p1</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Both scores below threshold produces priority = P4.</t>
+          <t>stat_score &gt;= 0.7 AND lit_score &gt;= 0.5 produces priority = P1.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1768,56 +1795,52 @@
       <c r="I28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>A3-05</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A3-02</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>test_priority_boundary_exact_thresholds</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Values exactly at boundary (stat=0.7, lit=0.5) are assigned to the higher tier (P1).</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Edge Case / Boundary</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>test_priority_tier_p2</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>stat_score &gt;= 0.7 AND lit_score &lt; 0.5 produces priority = P2.</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Boundary: inclusive threshold</t>
-        </is>
-      </c>
+      <c r="I29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>A3-06</t>
+          <t>A3-03</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1832,17 +1855,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>test_stat_score_fallback_formula</t>
+          <t>test_priority_tier_p3</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Agent 3 computes stat_score locally when Agent 1 did not supply it; PRR=4.0, 50 cases =&gt; ~0.70.</t>
+          <t>stat_score &lt; 0.7 AND lit_score &gt;= 0.5 produces priority = P3.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1855,423 +1878,419 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Fallback formula</t>
-        </is>
-      </c>
+      <c r="I30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>A3-04</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Agent 3 – Assessor</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>unit/test_agent3.py</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>test_priority_tier_p4</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Both scores below threshold produces priority = P4.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>A3-05</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Agent 3 – Assessor</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>unit/test_agent3.py</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>test_priority_boundary_exact_thresholds</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Values exactly at boundary (stat=0.7, lit=0.5) are assigned to the higher tier (P1).</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Boundary: inclusive threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A3-06</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Agent 3 – Assessor</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>unit/test_agent3.py</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>test_stat_score_fallback_formula</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Agent 3 computes stat_score locally when Agent 1 did not supply it; PRR=4.0, 50 cases =&gt; ~0.70.</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Fallback formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>A3-07</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>test_stat_score_death_increases_severity</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Adding a death flag raises the severity component of stat_score from 0.0 to 1.0.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>A3-08</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>test_stat_score_lt_higher_than_hosp</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Life-threatening events (weight 0.75) outrank hospitalisation (weight 0.50) in severity score.</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>A3-09</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>test_pydantic_rejects_missing_fields</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>SafetyBriefOutput rejects output with missing required fields — raises ValidationError.</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Invalid Input</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Invalid Input</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Schema validation</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>A3-10</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>test_pydantic_rejects_bad_recommended_action</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>recommended_action must be one of MONITOR / LABEL_UPDATE / RESTRICT / WITHDRAW — other values rejected.</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Invalid Input</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Invalid Input</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Schema validation</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>A3-11</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>test_pydantic_rejects_stat_score_out_of_range</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>stat_score outside [0.0, 1.0] is rejected by Pydantic validation.</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Invalid Input</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Invalid Input</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Range validation</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>A3-12</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>test_pydantic_accepts_valid_brief</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Correctly formed SafetyBriefOutput passes all Pydantic validation rules.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>A3-13</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Agent 3 – Assessor</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_agent3.py</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>test_citation_guard_removes_fabricated_pmids</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>PMIDs in the brief but absent from the retrieved abstract set are stripped before writing to Snowflake.</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Hallucination guard</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>A3-14</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Agent 3 – Assessor</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_agent3.py</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>test_citation_guard_allows_all_when_all_valid</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>No PMIDs removed when every cited PMID is contained in the retrieved abstract set.</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>A3-15</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Agent 3 – Assessor</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>unit/test_agent3.py</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>test_citation_guard_empty_retrieved</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>If Agent 2 returned zero abstracts, all PMIDs cited by GPT-4o are treated as fabricated and stripped.</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Edge Case</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Empty upstream</t>
-        </is>
-      </c>
+      <c r="I39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>A3-16</t>
+          <t>A3-13</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2286,17 +2305,17 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>test_agent3_uses_state_stat_score_when_present</t>
+          <t>test_citation_guard_removes_fabricated_pmids</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>If stat_score is already in state (from Agent 1), Agent 3 uses it verbatim without re-computing.</t>
+          <t>PMIDs in the brief but absent from the retrieved abstract set are stripped before writing to Snowflake.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2309,12 +2328,16 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Hallucination guard</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A3-17</t>
+          <t>A3-14</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2329,17 +2352,17 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>test_agent3_node_returns_required_state_keys</t>
+          <t>test_citation_guard_allows_all_when_all_valid</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>agent3_node returns a dict with at minimum 'priority' and 'brief' keys (GPT-4o and Snowflake mocked).</t>
+          <t>No PMIDs removed when every cited PMID is contained in the retrieved abstract set.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2352,110 +2375,102 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Mocked IO</t>
-        </is>
-      </c>
+      <c r="I41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>A3-18</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>A3-15</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>test_normalize_action_maps_prose_variants</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>_normalize_action maps GPT-4o prose variants (e.g. 'label update recommended') to valid literals.</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>test_citation_guard_empty_retrieved</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>If Agent 2 returned zero abstracts, all PMIDs cited by GPT-4o are treated as fabricated and stripped.</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>Normalisation</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Empty upstream</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>A3-19</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A3-16</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>test_agent3_node_sets_gen_error_on_double_failure</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>When both GPT-4o retry attempts return malformed JSON, agent3_node sets generation_error=True and returns brief=None.</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – GPT-4o Failure</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>test_agent3_uses_state_stat_score_when_present</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>If stat_score is already in state (from Agent 1), Agent 3 uses it verbatim without re-computing.</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>Double failure</t>
-        </is>
-      </c>
+      <c r="I43" s="5" t="inlineStr"/>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>A3-20</t>
+          <t>A3-17</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2465,69 +2480,69 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>integration/test_agent3.py</t>
+          <t>unit/test_agent3.py</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>test_agent3_full_run_bupropion</t>
+          <t>test_agent3_node_returns_required_state_keys</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>End-to-end Agent 3 with real GPT-4o and Snowflake: bupropion x seizure. Verifies priority, brief written, PMIDs valid, row persisted.</t>
+          <t>agent3_node returns a dict with at minimum 'priority' and 'brief' keys (GPT-4o and Snowflake mocked).</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Live GPT-4o + Snowflake</t>
+          <t>Mocked IO</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HC-01</t>
+          <t>A3-18</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Hallucination Detection</t>
+          <t>Agent 3 – Assessor</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>unit/test_hallucination_check.py</t>
+          <t>unit/test_agent3.py</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>test_numerical_accuracy_clean</t>
+          <t>test_normalize_action_maps_prose_variants</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Brief with correct PRR, case count, and death count produces hallucination_rate = 0.0.</t>
+          <t>_normalize_action maps GPT-4o prose variants (e.g. 'label update recommended') to valid literals.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2537,40 +2552,44 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr"/>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Normalisation</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>HC-02</t>
+          <t>A3-19</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Hallucination Detection</t>
+          <t>Agent 3 – Assessor</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>unit/test_hallucination_check.py</t>
+          <t>unit/test_agent3.py</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>test_numerical_accuracy_hallucinated_prr</t>
+          <t>test_agent3_node_sets_gen_error_on_double_failure</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Brief claims PRR = 10.5 but actual PRR = 3.5 — fabricated value detected, rate &gt; 0.</t>
+          <t>When both GPT-4o retry attempts return malformed JSON, agent3_node sets generation_error=True and returns brief=None.</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Sad Path – Hallucination</t>
+          <t>Negative Scenario – GPT-4o Failure</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -2580,293 +2599,297 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>PRR fabrication</t>
+          <t>Double failure</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>HC-03</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Hallucination Detection</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>unit/test_hallucination_check.py</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>test_numerical_accuracy_false_death_claim</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>Brief says 'no deaths reported' but data shows death_count = 5 — false claim detected.</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Hallucination</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Death count lie</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A3-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agent 3 – Assessor</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unit/test_agent3.py</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>test_agent3_llm_router_total_failure</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>When LLMRouter raises RuntimeError on every attempt, agent3_node sets error in state and writes generation_error=True to Snowflake.</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>Negative Scenario – LLM Failure</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Total LLM failure</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>HC-04</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Hallucination Detection</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_hallucination_check.py</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>test_priority_action_consistency_valid</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>P1 signal with LABEL_UPDATE and serious outcomes — consistent, hallucination_rate = 0.0.</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A3-21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agent 3 – Assessor</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unit/test_agent3.py</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>test_normalize_action_empty_string_defaults_to_monitor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>_normalize_action with an empty recommended_action string defaults to MONITOR without raising an exception.</t>
+        </is>
+      </c>
+      <c r="F48" s="25" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Invalid Input</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Empty action guard</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>HC-05</t>
+          <t>A3-22</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>Agent 3 – Assessor</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_agent3.py</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>test_agent3_full_run_bupropion</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>End-to-end Agent 3 with real GPT-4o and Snowflake: bupropion x seizure. Verifies priority, brief written, PMIDs valid, row persisted.</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Live GPT-4o + Snowflake</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>HC-01</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>test_priority_action_consistency_restrict_with_low_prr_deaths</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>RESTRICT with deaths and PRR = 2.98 (above the 2.0 threshold) — valid recommendation.</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>test_numerical_accuracy_clean</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Brief with correct PRR, case count, and death count produces hallucination_rate = 0.0.</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Boundary: PRR just above 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="40" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>HC-06</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>HC-02</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>test_priority_action_consistency_invalid_withdraw</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>WITHDRAW recommended for P4 with 0 deaths and PRR = 2.1 — three errors, rate = 1.0.</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Hallucination</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>test_numerical_accuracy_hallucinated_prr</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Brief claims PRR = 10.5 but actual PRR = 3.5 — fabricated value detected, rate &gt; 0.</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Hallucination</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Unjustified WITHDRAW</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="40" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>HC-07</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>PRR fabrication</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>HC-03</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>test_priority_action_consistency_monitor_mild_reaction</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>P1 signal with MONITOR for mild reaction (0 deaths, 0 LT, 0 hosp) — valid action, rate = 0.0.</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>test_numerical_accuracy_false_death_claim</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Brief says 'no deaths reported' but data shows death_count = 5 — false claim detected.</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Hallucination</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>Mild AE exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="40" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>HC-08</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Hallucination Detection</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>unit/test_hallucination_check.py</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>test_citation_grounding_no_abstracts</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>No abstracts available — grounding check skipped, hallucination_rate = 0.0 (data issue, not hallucination).</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Edge Case</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr"/>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Death count lie</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>HC-09</t>
+          <t>HC-04</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -2881,17 +2904,17 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>test_citation_grounding_with_valid_citations</t>
+          <t>test_priority_action_consistency_valid</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Brief cites a PMID with high semantic similarity to retrieved abstract — rate &lt; 0.5.</t>
+          <t>P1 signal with LABEL_UPDATE and serious outcomes — consistent, hallucination_rate = 0.0.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2904,16 +2927,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>Citation grounding</t>
-        </is>
-      </c>
+      <c r="I53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>HC-10</t>
+          <t>HC-05</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -2928,17 +2947,17 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>test_composite_validation_clean_brief</t>
+          <t>test_priority_action_consistency_restrict_with_low_prr_deaths</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Full validate_brief() on clean dupilumab x conjunctivitis brief — pass=True, composite score &lt; 0.20.</t>
+          <t>RESTRICT with deaths and PRR = 2.98 (above the 2.0 threshold) — valid recommendation.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2953,14 +2972,14 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Composite check</t>
+          <t>Boundary: PRR just above 2</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>HC-11</t>
+          <t>HC-06</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -2975,17 +2994,17 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>test_composite_validation_problematic_brief</t>
+          <t>test_priority_action_consistency_invalid_withdraw</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Full validate_brief() on brief with fabricated PRR=15, 500 cases, WITHDRAW at P4 — pass=False, score &gt; 0.20.</t>
+          <t>WITHDRAW recommended for P4 with 0 deaths and PRR = 2.1 — three errors, rate = 1.0.</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Sad Path – Hallucination</t>
+          <t>Negative Scenario – Hallucination</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -3000,39 +3019,39 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Multiple hallucinations</t>
+          <t>Unjustified WITHDRAW</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>HT-01</t>
+          <t>HC-07</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>HITL Queue</t>
+          <t>Hallucination Detection</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>unit/test_hitl.py</t>
+          <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>test_health_returns_ok</t>
+          <t>test_priority_action_consistency_monitor_mild_reaction</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>GET /health returns HTTP 200 with status='ok' (Snowflake mocked).</t>
+          <t>P1 signal with MONITOR for mild reaction (0 deaths, 0 LT, 0 hosp) — valid action, rate = 0.0.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3042,177 +3061,181 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Mild AE exception</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>HT-02</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>HITL Queue</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_hitl.py</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>test_health_is_fast</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Health check responds in &lt; 15 seconds (accommodates Snowflake cold-start latency).</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Latency SLA</t>
-        </is>
-      </c>
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>HC-08</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Hallucination Detection</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>unit/test_hallucination_check.py</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>test_citation_grounding_no_abstracts</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>No abstracts available — grounding check skipped, hallucination_rate = 0.0 (data issue, not hallucination).</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr"/>
     </row>
     <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>HT-03</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>HITL Queue</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>unit/test_hitl.py</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>test_post_decision_rejects_invalid_decision</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>POST /hitl/decisions with decision='MAYBE' returns 422 Unprocessable Entity.</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Invalid Input</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Input validation</t>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>HC-09</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Hallucination Detection</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>unit/test_hallucination_check.py</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>test_citation_grounding_with_valid_citations</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Brief cites a PMID with high semantic similarity to retrieved abstract — rate &lt; 0.5.</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Citation grounding</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>HT-04</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>HITL Queue</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>unit/test_hitl.py</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>test_post_decision_rejects_missing_drug_key</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>POST /hitl/decisions without drug_key field returns 422.</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Missing Field</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>HC-10</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Hallucination Detection</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>unit/test_hallucination_check.py</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>test_composite_validation_clean_brief</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Full validate_brief() on clean dupilumab x conjunctivitis brief — pass=True, composite score &lt; 0.20.</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Composite check</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>HT-05</t>
+          <t>HC-11</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>HITL Queue</t>
+          <t>Hallucination Detection</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>unit/test_hitl.py</t>
+          <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>test_post_decision_rejects_missing_pt</t>
+          <t>test_composite_validation_problematic_brief</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>POST /hitl/decisions without pt field returns 422.</t>
+          <t>Full validate_brief() on brief with fabricated PRR=15, 500 cases, WITHDRAW at P4 — pass=False, score &gt; 0.20.</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Sad Path – Missing Field</t>
+          <t>Negative Scenario – Hallucination</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -3222,15 +3245,19 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Multiple hallucinations</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>HT-06</t>
+          <t>HT-01</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3245,17 +3272,17 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>test_post_decision_accepts_lowercase</t>
+          <t>test_health_returns_ok</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Decision value 'approve' (lowercase) is accepted and normalised to 'APPROVE'.</t>
+          <t>GET /health returns HTTP 200 with status='ok' (Snowflake mocked).</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3268,16 +3295,12 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Case-insensitive</t>
-        </is>
-      </c>
+      <c r="I61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>HT-07</t>
+          <t>HT-02</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -3292,17 +3315,17 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>test_post_decision_reviewer_note_is_optional</t>
+          <t>test_health_is_fast</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Omitting reviewer_note from the request body does not cause a validation error.</t>
+          <t>Health check responds in &lt; 15 seconds (accommodates Snowflake cold-start latency).</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3317,151 +3340,147 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Optional field</t>
+          <t>Latency SLA</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>HT-08</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>HT-03</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>test_hitl_decision_model_all_valid_decisions</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>All three valid values APPROVE / REJECT / ESCALATE pass Pydantic validation.</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>test_post_decision_rejects_invalid_decision</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>POST /hitl/decisions with decision='MAYBE' returns 422 Unprocessable Entity.</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Invalid Input</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>All valid literals</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Input validation</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>HT-09</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>HT-04</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>test_hitl_decision_model_brief_id_is_optional</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>brief_id is Optional — omitting it produces no validation error.</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>test_post_decision_rejects_missing_drug_key</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>POST /hitl/decisions without drug_key field returns 422.</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Missing Field</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Optional field</t>
-        </is>
-      </c>
+      <c r="I64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="40" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>HT-10</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>HT-05</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>test_get_queue_returns_list</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>GET /hitl/queue always returns a JSON list, never a dict or null.</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>test_post_decision_rejects_missing_pt</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>POST /hitl/decisions without pt field returns 422.</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Missing Field</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr"/>
+      <c r="I65" s="10" t="inlineStr"/>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>HT-11</t>
+          <t>HT-06</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -3476,17 +3495,17 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>test_get_queue_returns_correct_shape</t>
+          <t>test_post_decision_accepts_lowercase</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Every item in the queue list contains the required fields including brief_id.</t>
+          <t>Decision value 'approve' (lowercase) is accepted and normalised to 'APPROVE'.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -3501,14 +3520,14 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Schema shape</t>
+          <t>Case-insensitive</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>HT-12</t>
+          <t>HT-07</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -3523,17 +3542,17 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>test_get_decisions_returns_list</t>
+          <t>test_post_decision_reviewer_note_is_optional</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>GET /hitl/decisions always returns a JSON list.</t>
+          <t>Omitting reviewer_note from the request body does not cause a validation error.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3546,12 +3565,16 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Optional field</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>HT-13</t>
+          <t>HT-08</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -3561,44 +3584,44 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>integration/test_hitl.py</t>
+          <t>unit/test_hitl.py</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>test_health_endpoint_live</t>
+          <t>test_hitl_decision_model_all_valid_decisions</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Live health check connects to real Snowflake and returns snowflake_version as connectivity proof.</t>
+          <t>Both valid values APPROVE / REJECT are accepted by the Pydantic model (ESCALATE has been removed from valid decisions).</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Live Snowflake</t>
+          <t>All valid literals</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>HT-14</t>
+          <t>HT-09</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -3608,40 +3631,44 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>integration/test_hitl.py</t>
+          <t>unit/test_hitl.py</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>test_get_queue_live</t>
+          <t>test_hitl_decision_model_brief_id_is_optional</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Live GET /hitl/queue returns a list of pending signals from real Snowflake.</t>
+          <t>brief_id is Optional — omitting it produces no validation error.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Optional field</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>HT-15</t>
+          <t>HT-10</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -3651,32 +3678,32 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>integration/test_hitl.py</t>
+          <t>unit/test_hitl.py</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>test_get_decisions_live</t>
+          <t>test_get_queue_returns_list</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Live GET /hitl/decisions returns full audit log from real Snowflake.</t>
+          <t>GET /hitl/queue always returns a JSON list, never a dict or null.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
@@ -3684,7 +3711,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>HT-16</t>
+          <t>HT-11</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3694,69 +3721,69 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>integration/test_hitl.py</t>
+          <t>unit/test_hitl.py</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>test_post_decision_live</t>
+          <t>test_get_queue_returns_correct_shape</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Live POST /hitl/decisions writes a real row to hitl_decisions and verifies with follow-up query.</t>
+          <t>Every item in the queue list contains the required fields including brief_id.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Writes to Snowflake</t>
+          <t>Schema shape</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>EV-01</t>
+          <t>HT-12</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Evaluation – Golden Signals</t>
+          <t>HITL Queue</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>unit/test_evaluation.py</t>
+          <t>unit/test_hitl.py</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>test_exactly_10_golden_signals</t>
+          <t>test_get_decisions_returns_list</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>GOLDEN_SIGNALS constant contains exactly 10 entries.</t>
+          <t>GET /hitl/decisions always returns a JSON list.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -3766,187 +3793,187 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="40" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>EV-02</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Evaluation – Golden Signals</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_evaluation.py</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>test_all_required_fields_present</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Every golden signal record has all required fields: drug_key, pt, fda_comm_date, fda_comm_label.</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Schema completeness</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HT-13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HITL Queue</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>unit/test_hitl.py</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>test_hitl_cache_invalidated_after_approve_decision</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>POST /hitl/decisions with APPROVE calls invalidate_signals() exactly once, clearing the signal list cache.</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Cache invalidation</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>EV-03</t>
+          <t>HT-14</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Evaluation – Golden Signals</t>
+          <t>HITL Queue</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>unit/test_evaluation.py</t>
+          <t>integration/test_hitl.py</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>test_all_10_golden_drugs_present</t>
+          <t>test_health_endpoint_live</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>All 10 expected drug keys are present in the golden signal set.</t>
+          <t>Live health check connects to real Snowflake and returns snowflake_version as connectivity proof.</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr"/>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Live Snowflake</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="40" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>EV-04</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Evaluation – Golden Signals</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>unit/test_evaluation.py</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>test_fda_comm_dates_are_date_objects</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>fda_comm_date values are Python date objects, not strings — type guard.</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Type Error</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Type guard</t>
-        </is>
-      </c>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>HT-15</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>HITL Queue</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_hitl.py</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>test_get_queue_live</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Live GET /hitl/queue returns a list of pending signals from real Snowflake.</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr"/>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>EV-05</t>
+          <t>HT-16</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Evaluation – Golden Signals</t>
+          <t>HITL Queue</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>unit/test_evaluation.py</t>
+          <t>integration/test_hitl.py</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>test_fda_comm_dates_in_2023_or_2024</t>
+          <t>test_get_decisions_live</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>All FDA communication dates fall in 2023 or 2024 (FAERS data year range).</t>
+          <t>Live GET /hitl/decisions returns full audit log from real Snowflake.</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
@@ -3954,54 +3981,54 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>EV-06</t>
+          <t>HT-17</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Evaluation – Golden Signals</t>
+          <t>HITL Queue</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>unit/test_evaluation.py</t>
+          <t>integration/test_hitl.py</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>test_no_duplicate_drug_pt_pairs</t>
+          <t>test_post_decision_live</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>No two golden signals share the same (drug_key, pt) pair.</t>
+          <t>Live POST /hitl/decisions writes a real row to hitl_decisions and verifies with follow-up query.</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Uniqueness</t>
+          <t>Writes to Snowflake</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>EV-07</t>
+          <t>EV-01</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4016,17 +4043,17 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>test_pt_values_are_lowercase</t>
+          <t>test_exactly_10_golden_signals</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>All pt values in the golden set are lowercase (must match FAERS normalisation).</t>
+          <t>GOLDEN_SIGNALS constant contains exactly 10 entries.</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4039,16 +4066,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>Normalisation</t>
-        </is>
-      </c>
+      <c r="I78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>EV-08</t>
+          <t>EV-02</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4063,17 +4086,17 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>test_drug_keys_are_lowercase</t>
+          <t>test_all_required_fields_present</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>All drug_key values in the golden set are lowercase.</t>
+          <t>Every golden signal record has all required fields: drug_key, pt, fda_comm_date, fda_comm_label.</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4088,14 +4111,14 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Normalisation</t>
+          <t>Schema completeness</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>EV-09</t>
+          <t>EV-03</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4110,17 +4133,17 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>test_fda_comm_labels_non_empty</t>
+          <t>test_all_10_golden_drugs_present</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>fda_comm_label is a non-empty string for every golden signal.</t>
+          <t>All 10 expected drug keys are present in the golden signal set.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4136,142 +4159,146 @@
       <c r="I80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="40" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>EV-10</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>EV-04</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>test_positive_lead_time</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>Lead-time computation returns positive days when detection precedes FDA communication.</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>test_fda_comm_dates_are_date_objects</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>fda_comm_date values are Python date objects, not strings — type guard.</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Type Error</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Type guard</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="40" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>EV-11</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>EV-05</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>test_negative_lead_time</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>Lead-time computation returns negative days when detection follows FDA communication.</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Late Detection</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>test_fda_comm_dates_in_2023_or_2024</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>All FDA communication dates fall in 2023 or 2024 (FAERS data year range).</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I82" s="10" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="40" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>EV-12</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>EV-06</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>test_zero_lead_time</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>Lead-time = 0 when detection date equals FDA communication date.</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>Edge Case / Boundary</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>test_no_duplicate_drug_pt_pairs</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>No two golden signals share the same (drug_key, pt) pair.</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Same-day boundary</t>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Uniqueness</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>EV-13</t>
+          <t>EV-07</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -4286,17 +4313,17 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>test_metformin_lead_time</t>
+          <t>test_pt_values_are_lowercase</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Metformin POC lead time is approximately 13 days (per project proposal).</t>
+          <t>All pt values in the golden set are lowercase (must match FAERS normalisation).</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -4309,12 +4336,16 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Normalisation</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>EV-14</t>
+          <t>EV-08</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -4329,17 +4360,17 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>test_dupilumab_lead_time</t>
+          <t>test_drug_keys_are_lowercase</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Dupilumab POC lead time is approximately 291 days (per project proposal).</t>
+          <t>All drug_key values in the golden set are lowercase.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4352,12 +4383,16 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Normalisation</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>EV-15</t>
+          <t>EV-09</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -4372,17 +4407,17 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>test_precision_all_flagged</t>
+          <t>test_fda_comm_labels_non_empty</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Precision = 1.0 when all 10 golden signals are flagged.</t>
+          <t>fda_comm_label is a non-empty string for every golden signal.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -4400,7 +4435,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>EV-16</t>
+          <t>EV-10</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -4415,17 +4450,17 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>test_precision_six_flagged</t>
+          <t>test_positive_lead_time</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Precision = 0.6 when only 6 of 10 golden signals are flagged.</t>
+          <t>Lead-time computation returns positive days when detection precedes FDA communication.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4438,16 +4473,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>Partial detection</t>
-        </is>
-      </c>
+      <c r="I87" s="5" t="inlineStr"/>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>EV-17</t>
+          <t>EV-11</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -4462,17 +4493,17 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>test_precision_zero_flagged</t>
+          <t>test_negative_lead_time</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>Precision = 0.0 when none of the golden signals are flagged.</t>
+          <t>Lead-time computation returns negative days when detection follows FDA communication.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>Sad Path – Zero Detection</t>
+          <t>Negative Scenario – Late Detection</t>
         </is>
       </c>
       <c r="G88" s="9" t="inlineStr">
@@ -4485,84 +4516,84 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>Worst-case</t>
-        </is>
-      </c>
+      <c r="I88" s="10" t="inlineStr"/>
     </row>
     <row r="89" ht="40" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>RD-01</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Redis Cache</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>unit/test_redis.py</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>test_signal_cache_key_no_priority</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Signal cache key without priority filter contains 'all' in the key string.</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr"/>
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>EV-12</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation – Golden Signals</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>unit/test_evaluation.py</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>test_zero_lead_time</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Lead-time = 0 when detection date equals FDA communication date.</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Same-day boundary</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>RD-02</t>
+          <t>EV-13</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Redis Cache</t>
+          <t>Evaluation – Golden Signals</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>unit/test_redis.py</t>
+          <t>unit/test_evaluation.py</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>test_signal_cache_key_with_priority</t>
+          <t>test_metformin_lead_time</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Signal cache key with priority='P1' contains 'P1' in the key string.</t>
+          <t>Metformin POC lead time is approximately 13 days (per project proposal).</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -4572,7 +4603,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr"/>
@@ -4580,32 +4611,32 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>RD-03</t>
+          <t>EV-14</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Redis Cache</t>
+          <t>Evaluation – Golden Signals</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>unit/test_redis.py</t>
+          <t>unit/test_evaluation.py</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>test_signal_cache_key_different_priorities_are_different</t>
+          <t>test_dupilumab_lead_time</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>P1 and P2 filters produce different cache keys (no collision).</t>
+          <t>Dupilumab POC lead time is approximately 291 days (per project proposal).</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4615,44 +4646,40 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Collision check</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr"/>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>RD-04</t>
+          <t>EV-15</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Redis Cache</t>
+          <t>Evaluation – Golden Signals</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>unit/test_redis.py</t>
+          <t>unit/test_evaluation.py</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>test_signal_cache_key_different_limits_are_different</t>
+          <t>test_precision_all_flagged</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Different row limits produce different cache keys.</t>
+          <t>Precision = 1.0 when all 10 golden signals are flagged.</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -4662,44 +4689,40 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Collision check</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>RD-05</t>
+          <t>EV-16</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Redis Cache</t>
+          <t>Evaluation – Golden Signals</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>unit/test_redis.py</t>
+          <t>unit/test_evaluation.py</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>test_brief_cache_key_format</t>
+          <t>test_precision_six_flagged</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Brief cache key contains both drug_key and pt as expected.</t>
+          <t>Precision = 0.6 when only 6 of 10 golden signals are flagged.</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4709,62 +4732,66 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Partial detection</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="40" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>RD-06</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Redis Cache</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>unit/test_redis.py</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>test_brief_cache_key_spaces_handled</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>Spaces in pt value do not break the cache key (no KeyError or encoding error).</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>Edge Case</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Space handling</t>
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>EV-17</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Evaluation – Golden Signals</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>unit/test_evaluation.py</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>test_precision_zero_flagged</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>Precision = 0.0 when none of the golden signals are flagged.</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Zero Detection</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Worst-case</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>RD-07</t>
+          <t>RD-01</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -4779,17 +4806,17 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>test_brief_cache_key_different_signals_are_different</t>
+          <t>test_signal_cache_key_no_priority</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Two different drug/pt pairs produce different cache keys.</t>
+          <t>Signal cache key without priority filter contains 'all' in the key string.</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4802,16 +4829,12 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Collision check</t>
-        </is>
-      </c>
+      <c r="I95" s="5" t="inlineStr"/>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>RD-08</t>
+          <t>RD-02</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -4821,44 +4844,40 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>integration/test_redis.py</t>
+          <t>unit/test_redis.py</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>test_redis_connection</t>
+          <t>test_signal_cache_key_with_priority</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Redis is reachable on localhost:6379 — ping returns True.</t>
+          <t>Signal cache key with priority='P1' contains 'P1' in the key string.</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>RD-09</t>
+          <t>RD-03</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -4868,87 +4887,91 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>integration/test_redis.py</t>
+          <t>unit/test_redis.py</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>test_cache_set_and_get</t>
+          <t>test_signal_cache_key_different_priorities_are_different</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Value stored with cache_set() is retrievable with cache_get() and all fields match.</t>
+          <t>P1 and P2 filters produce different cache keys (no collision).</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr"/>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Collision check</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="40" customHeight="1">
-      <c r="A98" s="9" t="inlineStr">
-        <is>
-          <t>RD-10</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>RD-04</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>integration/test_redis.py</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t>test_cache_get_missing_key_returns_none</t>
-        </is>
-      </c>
-      <c r="E98" s="10" t="inlineStr">
-        <is>
-          <t>cache_get() for a non-existent key returns None — no exception raised.</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Missing Key</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Graceful miss</t>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>test_signal_cache_key_different_limits_are_different</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Different row limits produce different cache keys.</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Collision check</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>RD-11</t>
+          <t>RD-05</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -4958,87 +4981,87 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>integration/test_redis.py</t>
+          <t>unit/test_redis.py</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>test_cache_delete</t>
+          <t>test_brief_cache_key_format</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Key is no longer retrievable after cache_delete() is called.</t>
+          <t>Brief cache key contains both drug_key and pt as expected.</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr"/>
     </row>
     <row r="100" ht="40" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>RD-12</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>RD-06</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>integration/test_redis.py</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>test_cache_ttl_respected</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>Value stored with TTL=2s expires and is gone after 3 seconds.</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>TTL expiry</t>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>unit/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>test_brief_cache_key_spaces_handled</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Spaces in pt value do not break the cache key (no KeyError or encoding error).</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>Space handling</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>RD-13</t>
+          <t>RD-07</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -5048,44 +5071,44 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>integration/test_redis.py</t>
+          <t>unit/test_redis.py</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>test_signal_cache_full_flow</t>
+          <t>test_brief_cache_key_different_signals_are_different</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Full signal cache lifecycle: miss -&gt; store -&gt; hit -&gt; invalidate_signals() -&gt; miss.</t>
+          <t>Two different drug/pt pairs produce different cache keys.</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Full flow</t>
+          <t>Collision check</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>RD-14</t>
+          <t>RD-08</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -5100,17 +5123,17 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>test_brief_cache_full_flow</t>
+          <t>test_redis_connection</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Full brief cache lifecycle: miss -&gt; store -&gt; hit -&gt; invalidate_brief() -&gt; miss.</t>
+          <t>Redis is reachable on localhost:6379 — ping returns True.</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -5125,14 +5148,14 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Full flow</t>
+          <t>Precondition</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>RD-15</t>
+          <t>RD-09</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -5147,17 +5170,17 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>test_queue_depth_set_and_get</t>
+          <t>test_cache_set_and_get</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>set_queue_depth(42) then get_queue_depth() returns 42.</t>
+          <t>Value stored with cache_set() is retrievable with cache_get() and all fields match.</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -5173,34 +5196,34 @@
       <c r="I103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="40" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>RD-16</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>RD-10</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>test_queue_depth_updates</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>Queue depth update from 100 to 99 is correctly stored (old value overwritten).</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>test_cache_get_missing_key_returns_none</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>cache_get() for a non-existent key returns None — no exception raised.</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Missing Key</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -5208,17 +5231,21 @@
           <t>Integration</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H104" s="9" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I104" s="5" t="inlineStr"/>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Graceful miss</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>RD-17</t>
+          <t>RD-11</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -5233,17 +5260,17 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>test_invalidate_signals_clears_all_priorities</t>
+          <t>test_cache_delete</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>invalidate_signals() clears ALL priority-filter keys (P1, P2, and no-filter) in a single call.</t>
+          <t>Key is no longer retrievable after cache_delete() is called.</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -5256,41 +5283,37 @@
           <t>live</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>Bulk invalidation</t>
-        </is>
-      </c>
+      <c r="I105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>OD-01</t>
+          <t>RD-12</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>On-Demand Pipeline</t>
+          <t>Redis Cache</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>integration/test_on_demand.py</t>
+          <t>integration/test_redis.py</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>test_known_signal_completes</t>
+          <t>test_cache_ttl_respected</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>run_single_signal('dupilumab', 'conjunctivitis') completes without exception or generation_error.</t>
+          <t>Value stored with TTL=2s expires and is gone after 3 seconds.</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
@@ -5300,44 +5323,44 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>live</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Golden signal</t>
+          <t>TTL expiry</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>OD-02</t>
+          <t>RD-13</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>On-Demand Pipeline</t>
+          <t>Redis Cache</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>integration/test_on_demand.py</t>
+          <t>integration/test_redis.py</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>test_priority_tier_valid</t>
+          <t>test_signal_cache_full_flow</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>dupilumab x conjunctivitis returns priority = P1.</t>
+          <t>Full signal cache lifecycle: miss -&gt; store -&gt; hit -&gt; invalidate_signals() -&gt; miss.</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -5347,44 +5370,44 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>live</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Known P1</t>
+          <t>Full flow</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>OD-03</t>
+          <t>RD-14</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>On-Demand Pipeline</t>
+          <t>Redis Cache</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>integration/test_on_demand.py</t>
+          <t>integration/test_redis.py</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>test_brief_generated</t>
+          <t>test_brief_cache_full_flow</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>SafetyBrief is not None and contains brief_text, key_findings, pmids_cited, recommended_action.</t>
+          <t>Full brief cache lifecycle: miss -&gt; store -&gt; hit -&gt; invalidate_brief() -&gt; miss.</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
@@ -5394,40 +5417,44 @@
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr"/>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>OD-04</t>
+          <t>RD-15</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>On-Demand Pipeline</t>
+          <t>Redis Cache</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>integration/test_on_demand.py</t>
+          <t>integration/test_redis.py</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>test_brief_content_valid</t>
+          <t>test_queue_depth_set_and_get</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>brief_text mentions 'dupilumab' and 'conjunctivitis'; key_findings non-empty; recommended_action is a valid literal.</t>
+          <t>set_queue_depth(42) then get_queue_depth() returns 42.</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -5437,44 +5464,40 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>Clinical correctness</t>
-        </is>
-      </c>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>OD-05</t>
+          <t>RD-16</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>On-Demand Pipeline</t>
+          <t>Redis Cache</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>integration/test_on_demand.py</t>
+          <t>integration/test_redis.py</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>test_scores_in_range</t>
+          <t>test_queue_depth_updates</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>stat_score and lit_score are both in [0.0, 1.0].</t>
+          <t>Queue depth update from 100 to 99 is correctly stored (old value overwritten).</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
@@ -5484,113 +5507,109 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Score bounds</t>
-        </is>
-      </c>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>OD-06</t>
+          <t>RD-17</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
+          <t>Redis Cache</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_redis.py</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>test_invalidate_signals_clears_all_priorities</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>invalidate_signals() clears ALL priority-filter keys (P1, P2, and no-filter) in a single call.</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Bulk invalidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>OD-01</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>test_snowflake_updated</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>After the run, Snowflake safety_briefs has a row for dupilumab x conjunctivitis with valid priority and generation_error=False.</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>test_known_signal_completes</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>run_single_signal('dupilumab', 'conjunctivitis') completes without exception or generation_error.</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>Persistence</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>OD-07</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>On-Demand Pipeline</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>integration/test_on_demand.py</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>test_nonexistent_signal_raises</t>
-        </is>
-      </c>
-      <c r="E112" s="10" t="inlineStr">
-        <is>
-          <t>run_single_signal('aspirin', 'headache') raises ValueError containing 'not found' (signal absent from signals_flagged).</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Sad Path – Invalid Signal</t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>integration</t>
-        </is>
-      </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>Signal not in DB</t>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Golden signal</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>OD-08</t>
+          <t>OD-02</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -5605,17 +5624,17 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>test_nongolden_signal_completes</t>
+          <t>test_priority_tier_valid</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>run_single_signal('tenofovir disoproxil', 'renal injury') completes without error — triggers on-demand PubMed fetch.</t>
+          <t>dupilumab x conjunctivitis returns priority = P1.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -5630,14 +5649,14 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Non-golden / on-demand fetch</t>
+          <t>Known P1</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>OD-09</t>
+          <t>OD-03</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -5652,17 +5671,17 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>test_nongolden_brief_generated</t>
+          <t>test_brief_generated</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Brief for tenofovir disoproxil x renal injury mentions 'tenofovir' and has a valid recommended_action.</t>
+          <t>SafetyBrief is not None and contains brief_text, key_findings, pmids_cited, recommended_action.</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
@@ -5680,32 +5699,32 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>SF-01</t>
+          <t>OD-04</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Snowflake Connector</t>
+          <t>On-Demand Pipeline</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>integration/test_snowflake_connector.py</t>
+          <t>integration/test_on_demand.py</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>test_python_connector</t>
+          <t>test_brief_content_valid</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>snowflake-connector-python connects to Snowflake and executes SELECT CURRENT_VERSION() successfully.</t>
+          <t>brief_text mentions 'dupilumab' and 'conjunctivitis'; key_findings non-empty; recommended_action is a valid literal.</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
@@ -5720,39 +5739,39 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Connectivity</t>
+          <t>Clinical correctness</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>SF-02</t>
+          <t>OD-05</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Snowflake Connector</t>
+          <t>On-Demand Pipeline</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>integration/test_snowflake_connector.py</t>
+          <t>integration/test_on_demand.py</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>test_spark_write</t>
+          <t>test_scores_in_range</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Spark writes a 3-row test DataFrame to Snowflake via JDBC without error.</t>
+          <t>stat_score and lit_score are both in [0.0, 1.0].</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
@@ -5767,54 +5786,505 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Write path</t>
+          <t>Score bounds</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
+          <t>OD-06</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>On-Demand Pipeline</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_on_demand.py</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>test_snowflake_updated</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>After the run, Snowflake safety_briefs has a row for dupilumab x conjunctivitis with valid priority and generation_error=False.</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>OD-07</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>On-Demand Pipeline</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>integration/test_on_demand.py</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>test_nonexistent_signal_raises</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>run_single_signal('aspirin', 'headache') raises ValueError containing 'not found' (signal absent from signals_flagged).</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Invalid Signal</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Signal not in DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>OD-08</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>On-Demand Pipeline</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_on_demand.py</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>test_nongolden_signal_completes</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>run_single_signal('tenofovir disoproxil', 'renal injury') completes without error — triggers on-demand PubMed fetch.</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Non-golden / on-demand fetch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>OD-09</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>On-Demand Pipeline</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_on_demand.py</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>test_nongolden_brief_generated</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Brief for tenofovir disoproxil x renal injury mentions 'tenofovir' and has a valid recommended_action.</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>SF-01</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Snowflake Connector</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_snowflake_connector.py</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>test_python_connector</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>snowflake-connector-python connects to Snowflake and executes SELECT CURRENT_VERSION() successfully.</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>SF-02</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Snowflake Connector</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>integration/test_snowflake_connector.py</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>test_spark_write</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Spark writes a 3-row test DataFrame to Snowflake via JDBC without error.</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Write path</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
           <t>SF-03</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>Snowflake Connector</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>integration/test_snowflake_connector.py</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>test_spark_read</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>Spark reads back the table written in test_spark_write and row count matches (round-trip verification).</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Happy Path</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr">
+      <c r="H123" s="4" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>Read path</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SA-01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Signal API</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>unit/test_signals_api.py</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>test_list_signals_has_hitl_decision_key</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Every item in GET /signals response has a hitl_decision key; validates the LEFT JOIN on hitl_decisions exposes the field.</t>
+        </is>
+      </c>
+      <c r="F124" s="26" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SA-02</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Signal API</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>unit/test_signals_api.py</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>test_signal_count_endpoint_shape</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>GET /signals/count returns a dict with integer keys: total, P1, P2, P3, P4, uninvestigated.</t>
+        </is>
+      </c>
+      <c r="F125" s="26" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SA-03</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Signal API</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>unit/test_signals_api.py</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>test_list_signals_priority_filter</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>GET /signals?priority=P1 returns only P1 signals; router correctly passes the priority filter to the service layer.</t>
+        </is>
+      </c>
+      <c r="F126" s="26" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SA-04</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Signal API</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>unit/test_signals_api.py</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>test_get_brief_returns_404_when_not_found</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>GET /signals/{drug_key}/{pt}/brief returns 404 when no SafetyBrief exists for the signal (Agent 3 not yet run).</t>
+        </is>
+      </c>
+      <c r="F127" s="25" t="inlineStr">
+        <is>
+          <t>Negative Scenario – Not Found</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Agent 3 not yet run</t>
         </is>
       </c>
     </row>
@@ -5833,7 +6303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5870,12 +6340,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Happy Paths</t>
+          <t>Positive Scenarios</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Sad Paths</t>
+          <t>Negative Scenarios</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -5896,7 +6366,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>0</v>
@@ -5905,13 +6375,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -5921,13 +6391,13 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>1</v>
@@ -5936,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -5946,7 +6416,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>1</v>
@@ -5955,13 +6425,13 @@
         <v>14</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -5996,13 +6466,13 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>3</v>
@@ -6011,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -6115,28 +6585,53 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Signal API</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>81</v>
-      </c>
-      <c r="C12" s="13" t="n">
+      <c r="B13" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>88</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="F12" s="13" t="n">
+      <c r="D13" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>113</v>
+      <c r="G13" s="13" t="n">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -6200,7 +6695,7 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Happy Path</t>
+          <t>Positive Scenario</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -6218,7 +6713,7 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Sad Path</t>
+          <t>Negative Scenario</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
@@ -6263,6 +6758,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
         <is>

--- a/docs/medsignal_test_scenarios.xlsx
+++ b/docs/medsignal_test_scenarios.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Catalogue" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,36 +27,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="001B5E20"/>
+      <color rgb="FF1B5E20"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000D47A1"/>
+      <color rgb="FF0D47A1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -66,7 +72,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -75,22 +81,59 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B5E20"/>
+        <fgColor rgb="FF1B5E20"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F8E9"/>
+        <fgColor rgb="FFF1F8E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
+        <fgColor rgb="FF2E7D32"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="FFC8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FBE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECEFF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCDD2"/>
+        <bgColor rgb="FFFFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor rgb="FFC8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,34 +143,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9FBE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECEFF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-        <bgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,23 +157,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
       </left>
       <right style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
       </right>
       <top style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBDBDBD"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -165,50 +206,20 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
       </right>
       <top style="thin">
-        <color rgb="00BDBDBD"/>
+        <color rgb="FFBDBDBD"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BDBDBD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BDBDBD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BDBDBD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BDBDBD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BDBDBD"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -233,9 +244,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -255,19 +263,38 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -630,439 +657,433 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I127"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I142"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" style="22" min="1" max="1"/>
+    <col width="26" customWidth="1" style="22" min="2" max="2"/>
+    <col width="36" customWidth="1" style="22" min="3" max="3"/>
+    <col width="44" customWidth="1" style="22" min="4" max="4"/>
+    <col width="72" customWidth="1" style="22" min="5" max="5"/>
+    <col width="28" customWidth="1" style="22" min="6" max="6"/>
+    <col width="14" customWidth="1" style="22" min="7" max="8"/>
+    <col width="36" customWidth="1" style="22" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MedSignal Platform  —  Test Scenario Catalogue</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="31.95" customHeight="1" s="22">
+      <c r="A1" s="21" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="22">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Positive Scenarios  |  Negative Scenarios  |  Edge Cases    Unit + Integration</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="22.05" customHeight="1" s="22">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Test File</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Test Function</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Path Type</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="40.05" customHeight="1" s="22">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>A1-01</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>test_golden_signal_dupilumab</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>GPT-4o generates 3 valid PubMed queries for dupilumab x conjunctivitis (golden signal); stat_score from state is not overwritten.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="40.05" customHeight="1" s="22">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>A1-02</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>test_high_severity_signal</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Generates valid queries for gabapentin x cardio-respiratory arrest (death_count=67, high-severity).</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="40.05" customHeight="1" s="22">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>A1-03</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>test_borderline_prr</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>PRR just at threshold (2.0) — minimal statistical strength — still produces 3 distinct queries.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Edge Case / Boundary</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Boundary: PRR=2.0</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="40.05" customHeight="1" s="22">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>A1-04</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>test_high_volume_signal</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>semaglutide x nausea with large case count — queries generated correctly.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="I8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="40.05" customHeight="1" s="22">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>A1-05</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>test_no_outcome_flags</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>All outcome flags (deaths, hosp, LT) are zero — queries still generated.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="I9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="40.05" customHeight="1" s="22">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A1-06</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>test_template_fallback</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>When GPT-4o is unavailable, _template_queries() returns 3 distinct fallback queries covering mechanistic, epidemiological, and clinical angles.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>No API call</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="40.05" customHeight="1" s="22">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>A1-07</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>test_query_uniqueness</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>All 3 queries returned by GPT-4o are distinct (no duplicate queries).</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="40.05" customHeight="1" s="22">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>A1-08</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent1.py</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>test_all_golden_drugs</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>All 10 golden-signal drugs produce 3 valid queries using template fallback — no crash for any drug.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Template; no API cost</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="40.05" customHeight="1" s="22">
       <c r="A13" t="inlineStr">
         <is>
           <t>A1-09</t>
@@ -1088,7 +1109,7 @@
           <t>Queries with fewer than 6 words fail _validate_queries; queries with exactly 6 words pass (MIN_QUERY_WORDS=6 boundary).</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>Negative Scenario</t>
         </is>
@@ -1109,324 +1130,324 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14" ht="40.05" customHeight="1" s="22">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>A2-01</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>test_lit_score_empty</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Empty abstracts list returns LitScore = 0.0 exactly.</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="I14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="40.05" customHeight="1" s="22">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>A2-02</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>test_lit_score_five_perfect</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>5 HNSW abstracts with similarity=0.95 produce LitScore &gt; 0.9 (expected ~0.965).</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Verifies HNSW relevance weighting</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="40.05" customHeight="1" s="22">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>A2-03</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>test_lit_score_one_lower_than_five</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>1 abstract scores lower than 5 abstracts at identical similarity — volume component matters.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="I16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="40.05" customHeight="1" s="22">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>A2-04</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>test_rrf_multi_query_wins</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Paper appearing in 2 query result sets ranks above paper appearing in only 1.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Core RRF logic</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="40.05" customHeight="1" s="22">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>A2-05</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>test_rrf_no_duplicates</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Same PMID from two result sets appears exactly once in fused output.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>De-duplication</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="19" ht="40.05" customHeight="1" s="22">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>A2-06</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>test_rrf_keeps_best_similarity</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>When same paper appears in two result sets, the entry with the lowest distance is kept.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="I19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="40.05" customHeight="1" s="22">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>A2-07</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent2.py</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>test_rrf_hnsw_and_bm25_same_paper_scores_highest</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Paper found by BOTH HNSW and BM25 ranks above papers found by only one retriever.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Hybrid retrieval</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="40" customHeight="1">
+    <row r="21" ht="40.05" customHeight="1" s="22">
       <c r="A21" t="inlineStr">
         <is>
           <t>A2-08</t>
@@ -1452,7 +1473,7 @@
           <t>BM25-only abstracts (no HNSW match) use BM25_ONLY_RELEVANCE_FALLBACK=0.65 for relevance; lit_score = 0.65x0.70 + volume x0.30.</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Positive Scenario</t>
         </is>
@@ -1473,7 +1494,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="40.05" customHeight="1" s="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>A2-09</t>
@@ -1499,7 +1520,7 @@
           <t>Mixed HNSW+BM25 abstracts: BM25 increases volume score but only HNSW cosine similarity contributes to relevance.</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>Positive Scenario</t>
         </is>
@@ -1520,1095 +1541,1095 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="23" ht="40.05" customHeight="1" s="22">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>A2-10</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>integration/test_agent2.py</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>test_chromadb_loaded</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>ChromaDB must contain &gt;= 1,800 abstracts before any live retrieval test proceeds.</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Precondition check</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="24" ht="40.05" customHeight="1" s="22">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>A2-11</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>integration/test_agent2.py</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>test_dupilumab_conjunctivitis</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Live hybrid retrieval for dupilumab x conjunctivitis returns &gt;= 3 abstracts above the 0.60 cosine threshold.</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Golden signal</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25" ht="40.05" customHeight="1" s="22">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>A2-12</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>integration/test_agent2.py</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>test_gabapentin_respiratory</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Live hybrid retrieval for gabapentin x respiratory arrest returns valid results.</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="I25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="40.05" customHeight="1" s="22">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>A2-13</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>integration/test_agent2.py</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>test_bm25_finds_different_papers_than_hnsw</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>BM25 and HNSW return at least some non-overlapping papers, confirming complementary retrieval value.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>Hybrid diversity</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="27" ht="40.05" customHeight="1" s="22">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>A2-14</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>integration/test_agent2.py</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>test_empty_queries_graceful</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Agent 2 handles empty query list (Agent 1 failure scenario) without crashing — returns empty list.</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Upstream Failure</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Graceful degradation</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="40.05" customHeight="1" s="22">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>A3-01</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>test_priority_tier_p1</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>stat_score &gt;= 0.7 AND lit_score &gt;= 0.5 produces priority = P1.</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="I28" s="3" t="n"/>
+    </row>
+    <row r="29" ht="40.05" customHeight="1" s="22">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>A3-02</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>test_priority_tier_p2</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>stat_score &gt;= 0.7 AND lit_score &lt; 0.5 produces priority = P2.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="I29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="40.05" customHeight="1" s="22">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>A3-03</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>test_priority_tier_p3</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>stat_score &lt; 0.7 AND lit_score &gt;= 0.5 produces priority = P3.</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="I30" s="3" t="n"/>
+    </row>
+    <row r="31" ht="40.05" customHeight="1" s="22">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>A3-04</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>test_priority_tier_p4</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Both scores below threshold produces priority = P4.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="I31" s="3" t="n"/>
+    </row>
+    <row r="32" ht="40.05" customHeight="1" s="22">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>A3-05</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>test_priority_boundary_exact_thresholds</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Values exactly at boundary (stat=0.7, lit=0.5) are assigned to the higher tier (P1).</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Edge Case / Boundary</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Boundary: inclusive threshold</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33" ht="40.05" customHeight="1" s="22">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>A3-06</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>test_stat_score_fallback_formula</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Agent 3 computes stat_score locally when Agent 1 did not supply it; PRR=4.0, 50 cases =&gt; ~0.70.</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>Fallback formula</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="34" ht="40.05" customHeight="1" s="22">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>A3-07</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>test_stat_score_death_increases_severity</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Adding a death flag raises the severity component of stat_score from 0.0 to 1.0.</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="I34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="40.05" customHeight="1" s="22">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>A3-08</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>test_stat_score_lt_higher_than_hosp</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Life-threatening events (weight 0.75) outrank hospitalisation (weight 0.50) in severity score.</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="I35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="40.05" customHeight="1" s="22">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>A3-09</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>test_pydantic_rejects_missing_fields</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>SafetyBriefOutput rejects output with missing required fields — raises ValidationError.</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Invalid Input</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Schema validation</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="37" ht="40.05" customHeight="1" s="22">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>A3-10</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>test_pydantic_rejects_bad_recommended_action</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>recommended_action must be one of MONITOR / LABEL_UPDATE / RESTRICT / WITHDRAW — other values rejected.</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Invalid Input</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Schema validation</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="38" ht="40.05" customHeight="1" s="22">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>A3-11</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>test_pydantic_rejects_stat_score_out_of_range</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>stat_score outside [0.0, 1.0] is rejected by Pydantic validation.</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Invalid Input</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>Range validation</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="39" ht="40.05" customHeight="1" s="22">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>A3-12</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>test_pydantic_accepts_valid_brief</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Correctly formed SafetyBriefOutput passes all Pydantic validation rules.</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="I39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="40.05" customHeight="1" s="22">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>A3-13</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>test_citation_guard_removes_fabricated_pmids</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>PMIDs in the brief but absent from the retrieved abstract set are stripped before writing to Snowflake.</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>Hallucination guard</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="40" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="41" ht="40.05" customHeight="1" s="22">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>A3-14</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>test_citation_guard_allows_all_when_all_valid</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>No PMIDs removed when every cited PMID is contained in the retrieved abstract set.</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="I41" s="3" t="n"/>
+    </row>
+    <row r="42" ht="40.05" customHeight="1" s="22">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>A3-15</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>test_citation_guard_empty_retrieved</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>If Agent 2 returned zero abstracts, all PMIDs cited by GPT-4o are treated as fabricated and stripped.</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Empty upstream</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="43" ht="40.05" customHeight="1" s="22">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>A3-16</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>test_agent3_uses_state_stat_score_when_present</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>If stat_score is already in state (from Agent 1), Agent 3 uses it verbatim without re-computing.</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44" ht="40" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="40.05" customHeight="1" s="22">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>A3-17</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>test_agent3_node_returns_required_state_keys</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>agent3_node returns a dict with at minimum 'priority' and 'brief' keys (GPT-4o and Snowflake mocked).</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>Mocked IO</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="40" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="45" ht="40.05" customHeight="1" s="22">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>A3-18</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>test_normalize_action_maps_prose_variants</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>_normalize_action maps GPT-4o prose variants (e.g. 'label update recommended') to valid literals.</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>Normalisation</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="40" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="46" ht="40.05" customHeight="1" s="22">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>A3-19</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>unit/test_agent3.py</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>test_agent3_node_sets_gen_error_on_double_failure</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>When both GPT-4o retry attempts return malformed JSON, agent3_node sets generation_error=True and returns brief=None.</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – GPT-4o Failure</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Double failure</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="40" customHeight="1">
+    <row r="47" ht="40.05" customHeight="1" s="22">
       <c r="A47" t="inlineStr">
         <is>
           <t>A3-20</t>
@@ -2634,7 +2655,7 @@
           <t>When LLMRouter raises RuntimeError on every attempt, agent3_node sets error in state and writes generation_error=True to Snowflake.</t>
         </is>
       </c>
-      <c r="F47" s="25" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>Negative Scenario – LLM Failure</t>
         </is>
@@ -2655,7 +2676,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="40" customHeight="1">
+    <row r="48" ht="40.05" customHeight="1" s="22">
       <c r="A48" t="inlineStr">
         <is>
           <t>A3-21</t>
@@ -2681,7 +2702,7 @@
           <t>_normalize_action with an empty recommended_action string defaults to MONITOR without raising an exception.</t>
         </is>
       </c>
-      <c r="F48" s="25" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>Negative Scenario – Invalid Input</t>
         </is>
@@ -2702,1103 +2723,1103 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="40" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="49" ht="40.05" customHeight="1" s="22">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>A3-22</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>integration/test_agent3.py</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>test_agent3_full_run_bupropion</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>End-to-end Agent 3 with real GPT-4o and Snowflake: bupropion x seizure. Verifies priority, brief written, PMIDs valid, row persisted.</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>Live GPT-4o + Snowflake</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="40" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="50" ht="40.05" customHeight="1" s="22">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>HC-01</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>test_numerical_accuracy_clean</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Brief with correct PRR, case count, and death count produces hallucination_rate = 0.0.</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="40" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="I50" s="3" t="n"/>
+    </row>
+    <row r="51" ht="40.05" customHeight="1" s="22">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>HC-02</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>test_numerical_accuracy_hallucinated_prr</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Brief claims PRR = 10.5 but actual PRR = 3.5 — fabricated value detected, rate &gt; 0.</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Hallucination</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>PRR fabrication</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="40" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+    <row r="52" ht="40.05" customHeight="1" s="22">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>HC-03</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>test_numerical_accuracy_false_death_claim</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>Brief says 'no deaths reported' but data shows death_count = 5 — false claim detected.</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Hallucination</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Death count lie</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="40" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="53" ht="40.05" customHeight="1" s="22">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>HC-04</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>test_priority_action_consistency_valid</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>P1 signal with LABEL_UPDATE and serious outcomes — consistent, hallucination_rate = 0.0.</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="40" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="I53" s="3" t="n"/>
+    </row>
+    <row r="54" ht="40.05" customHeight="1" s="22">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>HC-05</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>test_priority_action_consistency_restrict_with_low_prr_deaths</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>RESTRICT with deaths and PRR = 2.98 (above the 2.0 threshold) — valid recommendation.</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>Boundary: PRR just above 2</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="40" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
+    <row r="55" ht="40.05" customHeight="1" s="22">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>HC-06</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>test_priority_action_consistency_invalid_withdraw</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>WITHDRAW recommended for P4 with 0 deaths and PRR = 2.1 — three errors, rate = 1.0.</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Hallucination</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Unjustified WITHDRAW</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="40" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="56" ht="40.05" customHeight="1" s="22">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>HC-07</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>test_priority_action_consistency_monitor_mild_reaction</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>P1 signal with MONITOR for mild reaction (0 deaths, 0 LT, 0 hosp) — valid action, rate = 0.0.</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>Mild AE exception</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+    <row r="57" ht="40.05" customHeight="1" s="22">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>HC-08</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>test_citation_grounding_no_abstracts</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>No abstracts available — grounding check skipped, hallucination_rate = 0.0 (data issue, not hallucination).</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="I57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="40.05" customHeight="1" s="22">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>HC-09</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>test_citation_grounding_with_valid_citations</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Brief cites a PMID with high semantic similarity to retrieved abstract — rate &lt; 0.5.</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>Citation grounding</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="59" ht="40.05" customHeight="1" s="22">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>HC-10</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>test_composite_validation_clean_brief</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Full validate_brief() on clean dupilumab x conjunctivitis brief — pass=True, composite score &lt; 0.20.</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>Composite check</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="40" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="60" ht="40.05" customHeight="1" s="22">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>HC-11</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>unit/test_hallucination_check.py</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>test_composite_validation_problematic_brief</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>Full validate_brief() on brief with fabricated PRR=15, 500 cases, WITHDRAW at P4 — pass=False, score &gt; 0.20.</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Hallucination</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>Multiple hallucinations</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="40" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="61" ht="40.05" customHeight="1" s="22">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>HT-01</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>test_health_returns_ok</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>GET /health returns HTTP 200 with status='ok' (Snowflake mocked).</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62" ht="40" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="I61" s="3" t="n"/>
+    </row>
+    <row r="62" ht="40.05" customHeight="1" s="22">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>HT-02</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>test_health_is_fast</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Health check responds in &lt; 15 seconds (accommodates Snowflake cold-start latency).</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>Latency SLA</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="40" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
+    <row r="63" ht="40.05" customHeight="1" s="22">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>HT-03</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>test_post_decision_rejects_invalid_decision</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>POST /hitl/decisions with decision='MAYBE' returns 422 Unprocessable Entity.</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Invalid Input</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>Input validation</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
+    <row r="64" ht="40.05" customHeight="1" s="22">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>HT-04</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>test_post_decision_rejects_missing_drug_key</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>POST /hitl/decisions without drug_key field returns 422.</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Missing Field</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr"/>
-    </row>
-    <row r="65" ht="40" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="I64" s="8" t="n"/>
+    </row>
+    <row r="65" ht="40.05" customHeight="1" s="22">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>HT-05</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>test_post_decision_rejects_missing_pt</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>POST /hitl/decisions without pt field returns 422.</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Missing Field</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr"/>
-    </row>
-    <row r="66" ht="40" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="I65" s="8" t="n"/>
+    </row>
+    <row r="66" ht="40.05" customHeight="1" s="22">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>HT-06</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>test_post_decision_accepts_lowercase</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Decision value 'approve' (lowercase) is accepted and normalised to 'APPROVE'.</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>Case-insensitive</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="40" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="67" ht="40.05" customHeight="1" s="22">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>HT-07</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>test_post_decision_reviewer_note_is_optional</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Omitting reviewer_note from the request body does not cause a validation error.</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>Optional field</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="40" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="68" ht="40.05" customHeight="1" s="22">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>HT-08</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>test_hitl_decision_model_all_valid_decisions</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Both valid values APPROVE / REJECT are accepted by the Pydantic model (ESCALATE has been removed from valid decisions).</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>All valid literals</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="40" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="69" ht="40.05" customHeight="1" s="22">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>HT-09</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>test_hitl_decision_model_brief_id_is_optional</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>brief_id is Optional — omitting it produces no validation error.</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>Optional field</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="40" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="70" ht="40.05" customHeight="1" s="22">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>HT-10</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>test_get_queue_returns_list</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>GET /hitl/queue always returns a JSON list, never a dict or null.</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71" ht="40" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="I70" s="3" t="n"/>
+    </row>
+    <row r="71" ht="40.05" customHeight="1" s="22">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>HT-11</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>test_get_queue_returns_correct_shape</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Every item in the queue list contains the required fields including brief_id.</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>Schema shape</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="40" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72" ht="40.05" customHeight="1" s="22">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>HT-12</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>unit/test_hitl.py</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>test_get_decisions_returns_list</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>GET /hitl/decisions always returns a JSON list.</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73" ht="40" customHeight="1">
+      <c r="I72" s="3" t="n"/>
+    </row>
+    <row r="73" ht="40.05" customHeight="1" s="22">
       <c r="A73" t="inlineStr">
         <is>
           <t>HT-13</t>
@@ -3824,7 +3845,7 @@
           <t>POST /hitl/decisions with APPROVE calls invalidate_signals() exactly once, clearing the signal list cache.</t>
         </is>
       </c>
-      <c r="F73" s="26" t="inlineStr">
+      <c r="F73" s="20" t="inlineStr">
         <is>
           <t>Positive Scenario</t>
         </is>
@@ -3845,2271 +3866,2271 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="40" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="74" ht="40.05" customHeight="1" s="22">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>HT-14</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>integration/test_hitl.py</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>test_health_endpoint_live</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Live health check connects to real Snowflake and returns snowflake_version as connectivity proof.</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>Live Snowflake</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="40" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="75" ht="40.05" customHeight="1" s="22">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>HT-15</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>integration/test_hitl.py</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>test_get_queue_live</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Live GET /hitl/queue returns a list of pending signals from real Snowflake.</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76" ht="40" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="I75" s="3" t="n"/>
+    </row>
+    <row r="76" ht="40.05" customHeight="1" s="22">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>HT-16</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>integration/test_hitl.py</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>test_get_decisions_live</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Live GET /hitl/decisions returns full audit log from real Snowflake.</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77" ht="40" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="I76" s="3" t="n"/>
+    </row>
+    <row r="77" ht="40.05" customHeight="1" s="22">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>HT-17</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>integration/test_hitl.py</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>test_post_decision_live</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Live POST /hitl/decisions writes a real row to hitl_decisions and verifies with follow-up query.</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>Writes to Snowflake</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="40" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="78" ht="40.05" customHeight="1" s="22">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>EV-01</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>test_exactly_10_golden_signals</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>GOLDEN_SIGNALS constant contains exactly 10 entries.</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79" ht="40" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="I78" s="3" t="n"/>
+    </row>
+    <row r="79" ht="40.05" customHeight="1" s="22">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>EV-02</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>test_all_required_fields_present</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Every golden signal record has all required fields: drug_key, pt, fda_comm_date, fda_comm_label.</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>Schema completeness</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="40" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="80" ht="40.05" customHeight="1" s="22">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>EV-03</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>test_all_10_golden_drugs_present</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>All 10 expected drug keys are present in the golden signal set.</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81" ht="40" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
+      <c r="I80" s="3" t="n"/>
+    </row>
+    <row r="81" ht="40.05" customHeight="1" s="22">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>EV-04</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>test_fda_comm_dates_are_date_objects</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>fda_comm_date values are Python date objects, not strings — type guard.</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Type Error</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>Type guard</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="40" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="82" ht="40.05" customHeight="1" s="22">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>EV-05</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>test_fda_comm_dates_in_2023_or_2024</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>All FDA communication dates fall in 2023 or 2024 (FAERS data year range).</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr"/>
-    </row>
-    <row r="83" ht="40" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="I82" s="3" t="n"/>
+    </row>
+    <row r="83" ht="40.05" customHeight="1" s="22">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>EV-06</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>test_no_duplicate_drug_pt_pairs</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>No two golden signals share the same (drug_key, pt) pair.</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>Uniqueness</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="40" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="84" ht="40.05" customHeight="1" s="22">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>EV-07</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>test_pt_values_are_lowercase</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>All pt values in the golden set are lowercase (must match FAERS normalisation).</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>Normalisation</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="40" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
+    <row r="85" ht="40.05" customHeight="1" s="22">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>EV-08</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>test_drug_keys_are_lowercase</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>All drug_key values in the golden set are lowercase.</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>Normalisation</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="40" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="86" ht="40.05" customHeight="1" s="22">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>EV-09</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>test_fda_comm_labels_non_empty</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>fda_comm_label is a non-empty string for every golden signal.</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87" ht="40" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="I86" s="3" t="n"/>
+    </row>
+    <row r="87" ht="40.05" customHeight="1" s="22">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>EV-10</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>test_positive_lead_time</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Lead-time computation returns positive days when detection precedes FDA communication.</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88" ht="40" customHeight="1">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="I87" s="3" t="n"/>
+    </row>
+    <row r="88" ht="40.05" customHeight="1" s="22">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>EV-11</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>test_negative_lead_time</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Lead-time computation returns negative days when detection follows FDA communication.</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Late Detection</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr"/>
-    </row>
-    <row r="89" ht="40" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="I88" s="8" t="n"/>
+    </row>
+    <row r="89" ht="40.05" customHeight="1" s="22">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>EV-12</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>test_zero_lead_time</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>Lead-time = 0 when detection date equals FDA communication date.</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Edge Case / Boundary</t>
         </is>
       </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Same-day boundary</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="40" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="90" ht="40.05" customHeight="1" s="22">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>EV-13</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>test_metformin_lead_time</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Metformin POC lead time is approximately 13 days (per project proposal).</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91" ht="40" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="I90" s="3" t="n"/>
+    </row>
+    <row r="91" ht="40.05" customHeight="1" s="22">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>EV-14</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>test_dupilumab_lead_time</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Dupilumab POC lead time is approximately 291 days (per project proposal).</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92" ht="40" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="I91" s="3" t="n"/>
+    </row>
+    <row r="92" ht="40.05" customHeight="1" s="22">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>EV-15</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>test_precision_all_flagged</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>Precision = 1.0 when all 10 golden signals are flagged.</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr"/>
-    </row>
-    <row r="93" ht="40" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="I92" s="3" t="n"/>
+    </row>
+    <row r="93" ht="40.05" customHeight="1" s="22">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>EV-16</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>test_precision_six_flagged</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Precision = 0.6 when only 6 of 10 golden signals are flagged.</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>Partial detection</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="40" customHeight="1">
-      <c r="A94" s="9" t="inlineStr">
+    <row r="94" ht="40.05" customHeight="1" s="22">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>EV-17</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>unit/test_evaluation.py</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="8" t="inlineStr">
         <is>
           <t>test_precision_zero_flagged</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>Precision = 0.0 when none of the golden signals are flagged.</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Zero Detection</t>
         </is>
       </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>Worst-case</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="40" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="95" ht="40.05" customHeight="1" s="22">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>RD-01</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>test_signal_cache_key_no_priority</t>
         </is>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Signal cache key without priority filter contains 'all' in the key string.</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96" ht="40" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="I95" s="3" t="n"/>
+    </row>
+    <row r="96" ht="40.05" customHeight="1" s="22">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>RD-02</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>test_signal_cache_key_with_priority</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Signal cache key with priority='P1' contains 'P1' in the key string.</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97" ht="40" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="I96" s="3" t="n"/>
+    </row>
+    <row r="97" ht="40.05" customHeight="1" s="22">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>RD-03</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>test_signal_cache_key_different_priorities_are_different</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>P1 and P2 filters produce different cache keys (no collision).</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>Collision check</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="40" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98" ht="40.05" customHeight="1" s="22">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>RD-04</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>test_signal_cache_key_different_limits_are_different</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Different row limits produce different cache keys.</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t>Collision check</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="40" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+    <row r="99" ht="40.05" customHeight="1" s="22">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>RD-05</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>test_brief_cache_key_format</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Brief cache key contains both drug_key and pt as expected.</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr"/>
-    </row>
-    <row r="100" ht="40" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="I99" s="3" t="n"/>
+    </row>
+    <row r="100" ht="40.05" customHeight="1" s="22">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>RD-06</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>test_brief_cache_key_spaces_handled</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>Spaces in pt value do not break the cache key (no KeyError or encoding error).</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>Space handling</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="40" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="101" ht="40.05" customHeight="1" s="22">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>RD-07</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>unit/test_redis.py</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>test_brief_cache_key_different_signals_are_different</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Two different drug/pt pairs produce different cache keys.</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>Collision check</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="40" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="102" ht="40.05" customHeight="1" s="22">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>RD-08</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>test_redis_connection</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>Redis is reachable on localhost:6379 — ping returns True.</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="40" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="103" ht="40.05" customHeight="1" s="22">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>RD-09</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>test_cache_set_and_get</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Value stored with cache_set() is retrievable with cache_get() and all fields match.</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr"/>
-    </row>
-    <row r="104" ht="40" customHeight="1">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="I103" s="3" t="n"/>
+    </row>
+    <row r="104" ht="40.05" customHeight="1" s="22">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>RD-10</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>test_cache_get_missing_key_returns_none</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>cache_get() for a non-existent key returns None — no exception raised.</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Missing Key</t>
         </is>
       </c>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="G104" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H104" s="9" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>Graceful miss</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="40" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+    <row r="105" ht="40.05" customHeight="1" s="22">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>RD-11</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>test_cache_delete</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Key is no longer retrievable after cache_delete() is called.</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G105" s="8" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I105" s="5" t="inlineStr"/>
-    </row>
-    <row r="106" ht="40" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="I105" s="3" t="n"/>
+    </row>
+    <row r="106" ht="40.05" customHeight="1" s="22">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>RD-12</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>test_cache_ttl_respected</t>
         </is>
       </c>
-      <c r="E106" s="5" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Value stored with TTL=2s expires and is gone after 3 seconds.</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G106" s="8" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>TTL expiry</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="40" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
+    <row r="107" ht="40.05" customHeight="1" s="22">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>RD-13</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>test_signal_cache_full_flow</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>Full signal cache lifecycle: miss -&gt; store -&gt; hit -&gt; invalidate_signals() -&gt; miss.</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I107" s="5" t="inlineStr">
+      <c r="I107" s="3" t="inlineStr">
         <is>
           <t>Full flow</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="40" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="108" ht="40.05" customHeight="1" s="22">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>RD-14</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>test_brief_cache_full_flow</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>Full brief cache lifecycle: miss -&gt; store -&gt; hit -&gt; invalidate_brief() -&gt; miss.</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>Full flow</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="40" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
+    <row r="109" ht="40.05" customHeight="1" s="22">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>RD-15</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>test_queue_depth_set_and_get</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>set_queue_depth(42) then get_queue_depth() returns 42.</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr"/>
-    </row>
-    <row r="110" ht="40" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="I109" s="3" t="n"/>
+    </row>
+    <row r="110" ht="40.05" customHeight="1" s="22">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>RD-16</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>test_queue_depth_updates</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>Queue depth update from 100 to 99 is correctly stored (old value overwritten).</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I110" s="5" t="inlineStr"/>
-    </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="I110" s="3" t="n"/>
+    </row>
+    <row r="111" ht="40.05" customHeight="1" s="22">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>RD-17</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>integration/test_redis.py</t>
         </is>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>test_invalidate_signals_clears_all_priorities</t>
         </is>
       </c>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>invalidate_signals() clears ALL priority-filter keys (P1, P2, and no-filter) in a single call.</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>Bulk invalidation</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="112" ht="40.05" customHeight="1" s="22">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>OD-01</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>test_known_signal_completes</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>run_single_signal('dupilumab', 'conjunctivitis') completes without exception or generation_error.</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>Golden signal</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="113" ht="40.05" customHeight="1" s="22">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>OD-02</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>test_priority_tier_valid</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>dupilumab x conjunctivitis returns priority = P1.</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H113" s="4" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I113" s="3" t="inlineStr">
         <is>
           <t>Known P1</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
+    <row r="114" ht="40.05" customHeight="1" s="22">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>OD-03</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>test_brief_generated</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>SafetyBrief is not None and contains brief_text, key_findings, pmids_cited, recommended_action.</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr"/>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="I114" s="3" t="n"/>
+    </row>
+    <row r="115" ht="40.05" customHeight="1" s="22">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>OD-04</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>test_brief_content_valid</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>brief_text mentions 'dupilumab' and 'conjunctivitis'; key_findings non-empty; recommended_action is a valid literal.</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H115" s="4" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>Clinical correctness</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="116" ht="40.05" customHeight="1" s="22">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>OD-05</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>test_scores_in_range</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>stat_score and lit_score are both in [0.0, 1.0].</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>Score bounds</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="117" ht="40.05" customHeight="1" s="22">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>OD-06</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>test_snowflake_updated</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>After the run, Snowflake safety_briefs has a row for dupilumab x conjunctivitis with valid priority and generation_error=False.</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>Persistence</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+    <row r="118" ht="28.8" customHeight="1" s="22">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>OD-07</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D118" s="8" t="inlineStr">
         <is>
           <t>test_nonexistent_signal_raises</t>
         </is>
       </c>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>run_single_signal('aspirin', 'headache') raises ValueError containing 'not found' (signal absent from signals_flagged).</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>Negative Scenario – Invalid Signal</t>
         </is>
       </c>
-      <c r="G118" s="8" t="inlineStr">
+      <c r="G118" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H118" s="9" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I118" s="10" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Signal not in DB</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="119" ht="28.8" customHeight="1" s="22">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>OD-08</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>test_nongolden_signal_completes</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>run_single_signal('tenofovir disoproxil', 'renal injury') completes without error — triggers on-demand PubMed fetch.</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H119" s="4" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>Non-golden / on-demand fetch</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="120" ht="28.8" customHeight="1" s="22">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>OD-09</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>integration/test_on_demand.py</t>
         </is>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>test_nongolden_brief_generated</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>Brief for tenofovir disoproxil x renal injury mentions 'tenofovir' and has a valid recommended_action.</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G120" s="8" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I120" s="5" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="I120" s="3" t="n"/>
+    </row>
+    <row r="121" ht="28.8" customHeight="1" s="22">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>SF-01</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Snowflake Connector</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>integration/test_snowflake_connector.py</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>test_python_connector</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>snowflake-connector-python connects to Snowflake and executes SELECT CURRENT_VERSION() successfully.</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H121" s="4" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>Connectivity</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>SF-02</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Snowflake Connector</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>integration/test_snowflake_connector.py</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>test_spark_write</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>Spark writes a 3-row test DataFrame to Snowflake via JDBC without error.</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G122" s="8" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H122" s="4" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>Write path</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="123" ht="28.8" customHeight="1" s="22">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>SF-03</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Snowflake Connector</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>integration/test_snowflake_connector.py</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>test_spark_read</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Spark reads back the table written in test_spark_write and row count matches (round-trip verification).</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H123" s="4" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>integration</t>
         </is>
       </c>
-      <c r="I123" s="5" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>Read path</t>
         </is>
@@ -6141,7 +6162,7 @@
           <t>Every item in GET /signals response has a hitl_decision key; validates the LEFT JOIN on hitl_decisions exposes the field.</t>
         </is>
       </c>
-      <c r="F124" s="26" t="inlineStr">
+      <c r="F124" s="20" t="inlineStr">
         <is>
           <t>Positive Scenario</t>
         </is>
@@ -6183,7 +6204,7 @@
           <t>GET /signals/count returns a dict with integer keys: total, P1, P2, P3, P4, uninvestigated.</t>
         </is>
       </c>
-      <c r="F125" s="26" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
         <is>
           <t>Positive Scenario</t>
         </is>
@@ -6225,7 +6246,7 @@
           <t>GET /signals?priority=P1 returns only P1 signals; router correctly passes the priority filter to the service layer.</t>
         </is>
       </c>
-      <c r="F126" s="26" t="inlineStr">
+      <c r="F126" s="20" t="inlineStr">
         <is>
           <t>Positive Scenario</t>
         </is>
@@ -6267,7 +6288,7 @@
           <t>GET /signals/{drug_key}/{pt}/brief returns 404 when no SafetyBrief exists for the signal (Agent 3 not yet run).</t>
         </is>
       </c>
-      <c r="F127" s="25" t="inlineStr">
+      <c r="F127" s="19" t="inlineStr">
         <is>
           <t>Negative Scenario – Not Found</t>
         </is>
@@ -6285,6 +6306,711 @@
       <c r="I127" t="inlineStr">
         <is>
           <t>Agent 3 not yet run</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="29" t="inlineStr">
+        <is>
+          <t>PB-01</t>
+        </is>
+      </c>
+      <c r="B128" s="29" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D128" s="29" t="inlineStr">
+        <is>
+          <t>test_stat_score_always_in_valid_range</t>
+        </is>
+      </c>
+      <c r="E128" s="29" t="inlineStr">
+        <is>
+          <t>StatScore is ALWAYS between 0.0 and 1.0 across 50 random (PRR, case_count, deaths, lt, hosp) combinations.</t>
+        </is>
+      </c>
+      <c r="F128" s="29" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G128" s="29" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H128" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I128" s="29" t="inlineStr">
+        <is>
+          <t>50 random inputs via Hypothesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="30" t="inlineStr">
+        <is>
+          <t>PB-02</t>
+        </is>
+      </c>
+      <c r="B129" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C129" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D129" s="30" t="inlineStr">
+        <is>
+          <t>test_stat_score_deterministic</t>
+        </is>
+      </c>
+      <c r="E129" s="30" t="inlineStr">
+        <is>
+          <t>Same inputs always produce identical StatScore — no randomness in scoring function (100 random combinations).</t>
+        </is>
+      </c>
+      <c r="F129" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G129" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H129" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I129" s="30" t="inlineStr">
+        <is>
+          <t>100 random inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="29" t="inlineStr">
+        <is>
+          <t>PB-03</t>
+        </is>
+      </c>
+      <c r="B130" s="29" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C130" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D130" s="29" t="inlineStr">
+        <is>
+          <t>test_stat_score_monotonic_with_deaths</t>
+        </is>
+      </c>
+      <c r="E130" s="29" t="inlineStr">
+        <is>
+          <t>StatScore increases (or stays same) when death count increases by 10, holding PRR, case_count, lt, hosp constant.</t>
+        </is>
+      </c>
+      <c r="F130" s="29" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G130" s="29" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H130" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I130" s="29" t="inlineStr">
+        <is>
+          <t>Monotonicity invariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="29" t="inlineStr">
+        <is>
+          <t>PB-04</t>
+        </is>
+      </c>
+      <c r="B131" s="29" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C131" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D131" s="29" t="inlineStr">
+        <is>
+          <t>test_stat_score_monotonic_with_prr</t>
+        </is>
+      </c>
+      <c r="E131" s="29" t="inlineStr">
+        <is>
+          <t>StatScore increases when PRR increases from range [0.1,5.0] to [5.0,20.0], holding outcomes constant.</t>
+        </is>
+      </c>
+      <c r="F131" s="29" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G131" s="29" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H131" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I131" s="29" t="inlineStr">
+        <is>
+          <t>Monotonicity invariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="30" t="inlineStr">
+        <is>
+          <t>PB-05</t>
+        </is>
+      </c>
+      <c r="B132" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C132" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D132" s="30" t="inlineStr">
+        <is>
+          <t>test_priority_always_valid</t>
+        </is>
+      </c>
+      <c r="E132" s="30" t="inlineStr">
+        <is>
+          <t>Priority assignment always returns one of P1, P2, P3, P4 for any stat_score and lit_score in [0,1] (200 random pairs).</t>
+        </is>
+      </c>
+      <c r="F132" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G132" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H132" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I132" s="30" t="inlineStr">
+        <is>
+          <t>200 random inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="30" t="inlineStr">
+        <is>
+          <t>PB-06</t>
+        </is>
+      </c>
+      <c r="B133" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C133" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D133" s="30" t="inlineStr">
+        <is>
+          <t>test_priority_deterministic</t>
+        </is>
+      </c>
+      <c r="E133" s="30" t="inlineStr">
+        <is>
+          <t>Same stat_score + lit_score always yields the same priority tier — no randomness in assignment (100 random pairs).</t>
+        </is>
+      </c>
+      <c r="F133" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G133" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H133" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I133" s="30" t="inlineStr">
+        <is>
+          <t>100 random inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="30" t="inlineStr">
+        <is>
+          <t>PB-07</t>
+        </is>
+      </c>
+      <c r="B134" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D134" s="30" t="inlineStr">
+        <is>
+          <t>test_p1_requires_high_stat_and_lit</t>
+        </is>
+      </c>
+      <c r="E134" s="30" t="inlineStr">
+        <is>
+          <t>stat_score &gt;= 0.7 AND lit_score &gt;= 0.5 ALWAYS yields P1 (50 random combinations in that range).</t>
+        </is>
+      </c>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G134" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H134" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I134" s="30" t="inlineStr">
+        <is>
+          <t>P1 definition from CLAUDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="30" t="inlineStr">
+        <is>
+          <t>PB-08</t>
+        </is>
+      </c>
+      <c r="B135" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C135" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D135" s="30" t="inlineStr">
+        <is>
+          <t>test_p4_for_low_stat_and_lit</t>
+        </is>
+      </c>
+      <c r="E135" s="30" t="inlineStr">
+        <is>
+          <t>stat_score &lt; 0.69 AND lit_score &lt; 0.49 ALWAYS yields P4 — catch-all for weak signals (50 random combinations).</t>
+        </is>
+      </c>
+      <c r="F135" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G135" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H135" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I135" s="30" t="inlineStr">
+        <is>
+          <t>P4 definition from CLAUDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="29" t="inlineStr">
+        <is>
+          <t>PB-09</t>
+        </is>
+      </c>
+      <c r="B136" s="29" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C136" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D136" s="29" t="inlineStr">
+        <is>
+          <t>test_priority_monotonic_with_stat_score</t>
+        </is>
+      </c>
+      <c r="E136" s="29" t="inlineStr">
+        <is>
+          <t>Higher stat_score leads to same or better priority tier (lower P number), holding lit_score constant (100 random pairs).</t>
+        </is>
+      </c>
+      <c r="F136" s="29" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G136" s="29" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H136" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I136" s="29" t="inlineStr">
+        <is>
+          <t>Monotonicity invariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="30" t="inlineStr">
+        <is>
+          <t>PB-10</t>
+        </is>
+      </c>
+      <c r="B137" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C137" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D137" s="30" t="inlineStr">
+        <is>
+          <t>test_prr_always_positive</t>
+        </is>
+      </c>
+      <c r="E137" s="30" t="inlineStr">
+        <is>
+          <t>PRR = (A/(A+B)) / (C/(C+D)) is ALWAYS &gt; 0 for any valid positive integer A, B, C, D (200 random combinations).</t>
+        </is>
+      </c>
+      <c r="F137" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G137" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H137" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I137" s="30" t="inlineStr">
+        <is>
+          <t>200 random inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="29" t="inlineStr">
+        <is>
+          <t>PB-11</t>
+        </is>
+      </c>
+      <c r="B138" s="29" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C138" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D138" s="29" t="inlineStr">
+        <is>
+          <t>test_prr_increases_when_a_increases</t>
+        </is>
+      </c>
+      <c r="E138" s="29" t="inlineStr">
+        <is>
+          <t>PRR increases when A (drug-reaction pair count) increases by 10, holding B, C, D constant.</t>
+        </is>
+      </c>
+      <c r="F138" s="29" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G138" s="29" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H138" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I138" s="29" t="inlineStr">
+        <is>
+          <t>Monotonicity invariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="30" t="inlineStr">
+        <is>
+          <t>PB-12</t>
+        </is>
+      </c>
+      <c r="B139" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C139" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D139" s="30" t="inlineStr">
+        <is>
+          <t>test_prr_above_2_threshold_meaningful</t>
+        </is>
+      </c>
+      <c r="E139" s="30" t="inlineStr">
+        <is>
+          <t>When PRR &gt; 2, drug_proportion &gt; 2 * background_proportion — validates that the 2.0 threshold has semantic meaning.</t>
+        </is>
+      </c>
+      <c r="F139" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G139" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H139" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I139" s="30" t="inlineStr">
+        <is>
+          <t>Threshold semantics check</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="30" t="inlineStr">
+        <is>
+          <t>PB-13</t>
+        </is>
+      </c>
+      <c r="B140" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C140" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D140" s="30" t="inlineStr">
+        <is>
+          <t>test_hallucination_score_always_in_range</t>
+        </is>
+      </c>
+      <c r="E140" s="30" t="inlineStr">
+        <is>
+          <t>Hallucination score is ALWAYS between 0.0 and 1.0 for both clean briefs and briefs with factual errors.</t>
+        </is>
+      </c>
+      <c r="F140" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G140" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H140" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I140" s="30" t="inlineStr">
+        <is>
+          <t>Score range invariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="29" t="inlineStr">
+        <is>
+          <t>PB-14</t>
+        </is>
+      </c>
+      <c r="B141" s="29" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C141" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D141" s="29" t="inlineStr">
+        <is>
+          <t>test_hallucination_score_increases_with_errors</t>
+        </is>
+      </c>
+      <c r="E141" s="29" t="inlineStr">
+        <is>
+          <t>Hallucination score is strictly higher for a brief with wrong PRR + wrong recommended_action vs. a clean brief.</t>
+        </is>
+      </c>
+      <c r="F141" s="29" t="inlineStr">
+        <is>
+          <t>Edge Case / Boundary</t>
+        </is>
+      </c>
+      <c r="G141" s="29" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H141" s="29" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I141" s="29" t="inlineStr">
+        <is>
+          <t>Error detection monotonicity</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="30" t="inlineStr">
+        <is>
+          <t>PB-15</t>
+        </is>
+      </c>
+      <c r="B142" s="30" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="C142" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis/test_properties.py</t>
+        </is>
+      </c>
+      <c r="D142" s="30" t="inlineStr">
+        <is>
+          <t>test_hallucination_pass_consistent_with_threshold</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>hallucination_pass is always TRUE when score &lt; 0.20, FALSE otherwise — validates threshold consistency.</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="G142" s="30" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H142" s="30" t="inlineStr">
+        <is>
+          <t>hypothesis</t>
+        </is>
+      </c>
+      <c r="I142" s="30" t="inlineStr">
+        <is>
+          <t>Pass/fail threshold = 0.20</t>
         </is>
       </c>
     </row>
@@ -6303,288 +7029,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" style="22" min="1" max="1"/>
+    <col width="14" customWidth="1" style="22" min="2" max="2"/>
+    <col width="20" customWidth="1" style="22" min="3" max="3"/>
+    <col width="14" customWidth="1" style="22" min="4" max="4"/>
+    <col width="12" customWidth="1" style="22" min="5" max="5"/>
+    <col width="14" customWidth="1" style="22" min="6" max="6"/>
+    <col width="10" customWidth="1" style="22" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="28.05" customHeight="1" s="22">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Summary  —  Test Coverage by Component</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="22.05" customHeight="1" s="22">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Unit Tests</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Integration Tests</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Positive Scenarios</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Negative Scenarios</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Edge Cases</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="19.95" customHeight="1" s="22">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Agent 1 – Signal Detector</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="9" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="19.95" customHeight="1" s="22">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Agent 2 – Literature Retriever</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="9" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+    <row r="5" ht="19.95" customHeight="1" s="22">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Agent 3 – Assessor</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="9" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="19.95" customHeight="1" s="22">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Hallucination Detection</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="9" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="7" ht="19.95" customHeight="1" s="22">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>HITL Queue</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="9" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="8" ht="19.95" customHeight="1" s="22">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Evaluation – Golden Signals</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="9" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1" s="22">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Redis Cache</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="9" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="19.95" customHeight="1" s="22">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>On-Demand Pipeline</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="9" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="11" ht="19.95" customHeight="1" s="22">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Snowflake Connector</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="9" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="24" customHeight="1" s="22">
       <c r="A12" t="inlineStr">
         <is>
           <t>Signal API</t>
@@ -6610,28 +7336,53 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Property-Based Tests</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v>91</v>
-      </c>
-      <c r="C13" s="13" t="n">
+      <c r="B14" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>94</v>
-      </c>
-      <c r="E13" s="13" t="n">
+      <c r="D14" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="E14" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>123</v>
+      <c r="F14" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6649,178 +7400,176 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="1" customWidth="1" min="3" max="3"/>
-    <col width="1" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" style="22" min="1" max="1"/>
+    <col width="80" customWidth="1" style="22" min="2" max="2"/>
+    <col width="1" customWidth="1" style="22" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1" s="22">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Legend  —  Colour Key and Pytest Markers</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="19.95" customHeight="1" s="22">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Hex Code</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="14" t="n"/>
-      <c r="B3" s="15" t="inlineStr">
+    <row r="3" ht="19.95" customHeight="1" s="22">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>C8E6C9</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Positive Scenario</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Positive Scenario</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>Expected success — valid inputs, normal flow, correct output.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="18" t="n"/>
-      <c r="B4" s="15" t="inlineStr">
+    <row r="4" ht="19.95" customHeight="1" s="22">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>FFCDD2</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Negative Scenario</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>Failure scenario — invalid input, error condition, hallucination, graceful degradation.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="19" t="n"/>
-      <c r="B5" s="15" t="inlineStr">
+    <row r="5" ht="19.95" customHeight="1" s="22">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>FFF9C4</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Edge Case</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Boundary condition, empty input, zero value, or unusual-but-valid scenario.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="20" t="n"/>
-      <c r="B6" s="15" t="inlineStr">
+    <row r="6" ht="19.95" customHeight="1" s="22">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>BBDEFB</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Level column highlight — test requires a live external service.</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="8" ht="19.95" customHeight="1" s="22">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Pytest Markers</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+    <row r="9" ht="19.95" customHeight="1" s="22">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>@pytest.mark.unit</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Pure logic — no network calls, no DB, no API.  Run: poetry run pytest -m unit</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="19.95" customHeight="1" s="22">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>@pytest.mark.live</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Requires live ChromaDB or Redis.  Run: poetry run pytest -m live</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="24" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="27" t="n"/>
+    </row>
+    <row r="11" ht="19.95" customHeight="1" s="22">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>@pytest.mark.integration</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Requires Snowflake + OpenAI credentials.  Run: poetry run pytest -m integration</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="27" t="n"/>
+    </row>
+    <row r="12" ht="19.95" customHeight="1" s="22">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Custom test runner or unmarked test (not collected by default -m unit filter).</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="24" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
